--- a/04_AWS/障害ログ要約資料.xlsx
+++ b/04_AWS/障害ログ要約資料.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\望都\04_AWS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\learning_products\04_AWS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CAE55F-8D7F-48CD-8D95-6BCE8C953495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21A0579-E685-4DA9-A030-5EF1FF9F1F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="3" xr2:uid="{9019B611-1C86-4A47-96D6-76458B7705FA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="6" xr2:uid="{9019B611-1C86-4A47-96D6-76458B7705FA}"/>
   </bookViews>
   <sheets>
     <sheet name="全体構成図" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="528">
   <si>
     <t>【1. 重大エラーの一覧】</t>
   </si>
@@ -373,12 +373,6 @@
     <t xml:space="preserve">      "Resource": [</t>
   </si>
   <si>
-    <t xml:space="preserve">        "arn:aws:s3:::log-summary-input",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        "arn:aws:s3:::log-summary-input/*"</t>
-  </si>
-  <si>
     <t xml:space="preserve">      ]</t>
   </si>
   <si>
@@ -388,9 +382,6 @@
     <t xml:space="preserve">        "s3:PutObject"</t>
   </si>
   <si>
-    <t xml:space="preserve">        "arn:aws:s3:::log-summary-output/*"</t>
-  </si>
-  <si>
     <t xml:space="preserve">  ]</t>
   </si>
   <si>
@@ -822,18 +813,12 @@
     </r>
   </si>
   <si>
-    <t>■ Public Subnet（10.0.1.0/24, 10.0.2.0/24）</t>
-  </si>
-  <si>
     <t>NAT Gateway（必要なら）</t>
   </si>
   <si>
     <t>ALB（今回は不要）</t>
   </si>
   <si>
-    <t>■ Private Subnet（10.0.11.0/24, 10.0.12.0/24）</t>
-  </si>
-  <si>
     <t>Lambda（ログ要約処理）</t>
   </si>
   <si>
@@ -911,21 +896,6 @@
   </si>
   <si>
     <t>Lambda のログ出力も閉域化。</t>
-  </si>
-  <si>
-    <r>
-      <t>名前：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>log-summary-input</t>
-    </r>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
@@ -955,10 +925,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>OUTPUT_BUCKET = log-summary-output</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>MODEL_ID = anthropic.claude-3-5-sonnet-20240620</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -967,210 +933,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>VPC: 10.0.0.0/16</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>├─</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Public Subnet A:  10.0.1.0/24  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NAT Gateway</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配置）</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>├─</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Public Subnet C:  10.0.2.0/24  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NAT Gateway</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配置）</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>├─</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Private Subnet A: 10.0.11.0/24 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lambda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配置）</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>└─</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Private Subnet C: 10.0.12.0/24 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lambda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配置）</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>カテゴリ</t>
   </si>
   <si>
@@ -1186,9 +948,6 @@
     <t>入力ログ</t>
   </si>
   <si>
-    <t>log-summary-input</t>
-  </si>
-  <si>
     <t>ビルドログをアップロードするバケット</t>
   </si>
   <si>
@@ -1201,9 +960,6 @@
     <t>S3プレフィックス</t>
   </si>
   <si>
-    <t>raw-logs/</t>
-  </si>
-  <si>
     <t>Lambdaトリガー対象のログ格納フォルダ</t>
   </si>
   <si>
@@ -1219,9 +975,6 @@
     <t>ログ要約処理</t>
   </si>
   <si>
-    <t>LogProcessor</t>
-  </si>
-  <si>
     <t>ログを読み込みBedrockで要約するLambda</t>
   </si>
   <si>
@@ -1231,9 +984,6 @@
     <t>Lambda実行ロール</t>
   </si>
   <si>
-    <t>LambdaLogSummaryExecutionRole</t>
-  </si>
-  <si>
     <t>LambdaがS3/Bedrockにアクセスするためのロール</t>
   </si>
   <si>
@@ -1243,9 +993,6 @@
     <t>S3アクセス</t>
   </si>
   <si>
-    <t>log-summary-input/outputへの最小権限アクセス</t>
-  </si>
-  <si>
     <t>Bedrockアクセス</t>
   </si>
   <si>
@@ -1270,9 +1017,6 @@
     <t>VPC名</t>
   </si>
   <si>
-    <t>log-summary-vpc</t>
-  </si>
-  <si>
     <t>ログ要約基盤専用VPC</t>
   </si>
   <si>
@@ -1282,24 +1026,15 @@
     <t>Private Subnet A</t>
   </si>
   <si>
-    <t>log-summary-private-a</t>
-  </si>
-  <si>
     <t>Lambda配置用</t>
   </si>
   <si>
     <t>Private Subnet C</t>
   </si>
   <si>
-    <t>log-summary-private-c</t>
-  </si>
-  <si>
     <t>Public Subnet A</t>
   </si>
   <si>
-    <t>log-summary-public-a</t>
-  </si>
-  <si>
     <t>NAT等を配置（必要時）</t>
   </si>
   <si>
@@ -1312,18 +1047,12 @@
     <t>Public RT</t>
   </si>
   <si>
-    <t>log-summary-public-rt</t>
-  </si>
-  <si>
     <t>Public Subnet用</t>
   </si>
   <si>
     <t>Private RT</t>
   </si>
   <si>
-    <t>log-summary-private-rt</t>
-  </si>
-  <si>
     <t>Private Subnet用</t>
   </si>
   <si>
@@ -1354,9 +1083,6 @@
     <t>ロググループ名</t>
   </si>
   <si>
-    <t>/aws/lambda/LogProcessor</t>
-  </si>
-  <si>
     <t>Lambdaログ出力先</t>
   </si>
   <si>
@@ -1366,16 +1092,10 @@
     <t>S3暗号化</t>
   </si>
   <si>
-    <t>kms-log-summary-s3</t>
-  </si>
-  <si>
     <t>S3バケット暗号化用</t>
   </si>
   <si>
     <t>Lambda暗号化（任意）</t>
-  </si>
-  <si>
-    <t>kms-log-summary-lambda</t>
   </si>
   <si>
     <t>Lambda環境変数暗号化用</t>
@@ -1405,10 +1125,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>⑦VPC：log-summary-vpc</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>⑨作成</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1428,9 +1144,6 @@
     <t>⑤サービス名に「s3」と入力→com.amazonaws.ap-northeast-1.s3を選択</t>
   </si>
   <si>
-    <t>⑧ルートテーブルを選択→PrivateRouteTable（log-summary-private-rt）を選ぶ</t>
-  </si>
-  <si>
     <t>⑤サービス名に「bedrock」と入力→ 以下の 2 つを順番に作成</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1468,8 +1181,11 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>VPC：</t>
+    <t>サブネット：</t>
+  </si>
+  <si>
+    <r>
+      <t>セキュリティグループ： → Lambda が所属する SG（例：</t>
     </r>
     <r>
       <rPr>
@@ -1478,23 +1194,6 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t>log-summary-vpc</t>
-    </r>
-  </si>
-  <si>
-    <t>サブネット：</t>
-  </si>
-  <si>
-    <r>
-      <t>セキュリティグループ： → Lambda が所属する SG（例：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
       <t>log-summary-lambda-sg</t>
     </r>
     <r>
@@ -1528,10 +1227,6 @@
   </si>
   <si>
     <t>共通設定（両方とも）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>log-summary-private-a</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1554,10 +1249,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>④VPC：log-summary-vpc</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>⑤サブネット：</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1570,9 +1261,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>log-summary-lambda-sg</t>
-  </si>
-  <si>
     <t>①Lambda → 対象関数 → 設定</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1589,58 +1277,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>vpce-s3-log-summary</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>vpce-bedrock-log-summary</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LambdaLogSummaryS3Access</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LambdaLogSummaryBedrockAccess</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>EC2アクセス</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>LambdaLogSummaryEC2Access</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>EC2 ENI 作成権限</t>
-  </si>
-  <si>
-    <t>log-summary-private-c</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>log-summary-public-c</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>vpce-logs-log-summary</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>3. バケット：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>log-summary-input</t>
-    </r>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
@@ -1673,10 +1314,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>vpce-bedrock-runtime-log-summary</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t># --- AWS クライアント ---</t>
   </si>
   <si>
@@ -1698,9 +1335,6 @@
     <t>            }</t>
   </si>
   <si>
-    <t>        ),</t>
-  </si>
-  <si>
     <t>    }</t>
   </si>
   <si>
@@ -6811,9 +6445,6 @@
     <t>TCP</t>
   </si>
   <si>
-    <t>sg-bedrock-endpoint-sg</t>
-  </si>
-  <si>
     <t>Bedrock Runtime endpointへの通信を許可</t>
   </si>
   <si>
@@ -6823,9 +6454,6 @@
     <t>デフォルトの全許可（必要に応じて制限可能）</t>
   </si>
   <si>
-    <t>bedrock-endpoint-sg</t>
-  </si>
-  <si>
     <t>sg-log-summary-lambda-sg</t>
   </si>
   <si>
@@ -6833,32 +6461,6 @@
   </si>
   <si>
     <t>エンドポイントからの応答を許可</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. PCから </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>log-summary-input/raw-logs/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> にログをアップロード</t>
-    </r>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1. VPC 全体構成（CIDR / サブネット）</t>
@@ -6921,17 +6523,233 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">                                                                                        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>┌──────────────┐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">   </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>┌──────────────┐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Public Subnet             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Public Subnet             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="ＭＳ ゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>　　　　　　　　　</t>
+      <t>・</t>
     </r>
     <r>
       <rPr>
@@ -6940,17 +6758,16 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> VPC (10.0.0.0/16)        </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　　　</t>
+      <t xml:space="preserve">NAT GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">            </t>
     </r>
     <r>
       <rPr>
@@ -6959,6 +6776,372 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">NAT GW </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">               </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>└──────────────┘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>└──────────────┘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>┌───────────────────────────────┐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">          Private Subnet A                                       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">S3 Gateway Endpoint </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">       </t>
     </r>
     <r>
@@ -6989,7 +7172,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">                                                                                        </t>
+      <t xml:space="preserve">  </t>
     </r>
     <r>
       <rPr>
@@ -7000,6 +7183,118 @@
       </rPr>
       <t>│</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lambda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Log Processor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                         </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -7028,7 +7323,7 @@
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
-      <t>┌──────────────┐</t>
+      <t>│</t>
     </r>
     <r>
       <rPr>
@@ -7043,10 +7338,38 @@
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Bedrock Interface Endpoint </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                          </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
         <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
       </rPr>
-      <t>┌──────────────┐</t>
+      <t>│</t>
     </r>
     <r>
       <rPr>
@@ -7055,6 +7378,148 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Logs Interface Endpoint </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>└───────────────────────────────┘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">      </t>
     </r>
     <r>
@@ -7103,7 +7568,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Public Subnet             </t>
+      <t xml:space="preserve">          Private Subnet C                                       </t>
     </r>
     <r>
       <rPr>
@@ -7121,16 +7586,103 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>│</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">   </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lambda</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">AZ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>冗長）</t>
     </r>
     <r>
       <rPr>
@@ -7139,1268 +7691,7 @@
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Public Subnet             </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10.0.1.0/24                </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 10.0.2.0/24                 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">              </t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">NAT GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">            </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">NAT GW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">               </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>└──────────────┘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>└──────────────┘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>┌───────────────────────────────┐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">          Private Subnet A                                       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">            10.0.11.0/24                                           </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">S3 Gateway Endpoint </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lambda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Log Processor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                         </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">     </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Bedrock Interface Endpoint </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                          </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Logs Interface Endpoint </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                                </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>└───────────────────────────────┘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">          Private Subnet C                                       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Lambda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">AZ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>冗長）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">                                    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-      </rPr>
-      <t>│</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">            10.0.12.0/24                                           </t>
     </r>
     <r>
       <rPr>
@@ -8668,13 +7959,146 @@
   <si>
     <t xml:space="preserve"> AWS コンソールでのデプロイ手順</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. バケット：xxx-xxxxxxxx-xxxxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "arn:aws:s3:::xxx-xxxxxxxx-xxxxx/*"</t>
+  </si>
+  <si>
+    <t>xxx-xxxxxxxx-xxxxx</t>
+  </si>
+  <si>
+    <t>名前：xxx-xxxxxxxx-xxxxx</t>
+  </si>
+  <si>
+    <t>xxx-xxxxxxxx-xxxxx/xxxxxへの最小権限アクセス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⑦VPC：xxx-xxxxxxxx-xxx</t>
+  </si>
+  <si>
+    <t>VPC：xxx-xxxxxxxx-xxx</t>
+  </si>
+  <si>
+    <t>④VPC：xxx-xxxxxxxx-xxx</t>
+  </si>
+  <si>
+    <t>xxx-xxxxxxxx-xxx</t>
+  </si>
+  <si>
+    <t>⑧ルートテーブルを選択→PrivateRouteTable（lxx-xxxxxxx-xxxxxxx-rt）を選ぶ</t>
+  </si>
+  <si>
+    <t>lxx-xxxxxxx-xxxxxxx-a</t>
+  </si>
+  <si>
+    <t>lxx-xxxxxxx-xxxxxxx-c</t>
+  </si>
+  <si>
+    <t>lxx-xxxxxxx-xxxxxxx-rt</t>
+  </si>
+  <si>
+    <t>xxxx-xx-xxx-xxxxxxx</t>
+  </si>
+  <si>
+    <t>xxxx-xxxxxxx-xxx-xxxxxxx</t>
+  </si>
+  <si>
+    <t>xxxx-xxxx-xxx-xxxxxxx</t>
+  </si>
+  <si>
+    <t>xxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxx-xxx-xxxxxxx-xx</t>
+  </si>
+  <si>
+    <t>xxx-xxx-xxxxxxx-xxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/xxx/xxxxxx/xxxxxxxxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VPC: xx.x.0.0/16</t>
+  </si>
+  <si>
+    <t>├─ Public Subnet A:  xx.x.1.0/24  （NAT Gateway配置）</t>
+  </si>
+  <si>
+    <t>├─ Public Subnet C:  xx.x.2.0/24  （NAT Gateway配置）</t>
+  </si>
+  <si>
+    <t>├─ Private Subnet A: xx.x.11.0/24 （Lambda配置）</t>
+  </si>
+  <si>
+    <t>└─ Private Subnet C: xx.x.12.0/24 （Lambda配置）</t>
+  </si>
+  <si>
+    <t>■ Public Subnet（xx.x.1.0/24, xx.x.2.0/24）</t>
+  </si>
+  <si>
+    <t>■ Private Subnet（xx.x.11.0/24, xx.x.12.0/24）</t>
+  </si>
+  <si>
+    <t>│   　　　　　　　　　 VPC (xx.x.0.0/16)        　　　       │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">│  │ xx.x.1.0/24                │   │ xx.x.2.0/24                 │     │              </t>
+  </si>
+  <si>
+    <t>│  │            xx.x.11.0/24                                           │       │</t>
+  </si>
+  <si>
+    <t>│  │            xx.x.12.0/24                                           │       │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        "arn:aws:s3:::xxx-xxxxxxxx-xxxxx",</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        "arn:aws:s3:::xxx-xxxxxxxx-xxxxx/*"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxx-xxxxxx-xxxxxx</t>
+  </si>
+  <si>
+    <t>OUTPUT_BUCKET = xxx-xxxxxx-xxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. PCから xxx-xxxxxxxx-xxxxx/xxx-xxxx/ にログをアップロード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxxxxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxx-xxx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>xxxx-xxxxxxx-xxxxxxx-xxx-xxxxxxx</t>
+  </si>
+  <si>
+    <t>xxx-xxxxxxx-xxxxxx-xx</t>
+  </si>
+  <si>
+    <t>xxxxxx-xxxxxxx-xx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8846,13 +8270,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
@@ -9171,7 +8588,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9265,9 +8682,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -9356,6 +8770,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9672,7 +9104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D88B1A68-559A-4E29-A952-86D89A7C8B14}">
-  <dimension ref="A2:A42"/>
+  <dimension ref="A2:C42"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="63.296875" bestFit="1" customWidth="1"/>
@@ -9753,82 +9185,88 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -9891,81 +9329,94 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B880E43-E004-4F1E-919D-E69879643A25}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="27.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="37" t="s">
-        <v>119</v>
+      <c r="A7" s="36" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="37" t="s">
-        <v>120</v>
+      <c r="A8" s="36" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="37" t="s">
-        <v>121</v>
+      <c r="A9" s="36" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="36" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="37" t="s">
-        <v>118</v>
+      <c r="A11" s="36" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="36" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="37" t="s">
-        <v>114</v>
+      <c r="A13" s="36" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="52" t="s">
-        <v>115</v>
-      </c>
+      <c r="A14" s="51" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -9975,7 +9426,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE76E02-3CE0-4EFD-8092-4295DDA18AEE}">
-  <dimension ref="A2:C5"/>
+  <dimension ref="A2:C53"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="24.09765625" customWidth="1"/>
@@ -9985,47 +9436,53 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>520</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3">
         <v>4000</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="64"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -10035,890 +9492,896 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38F76F1-AA20-4E9D-9856-2D950A56B526}">
-  <dimension ref="A1:A192"/>
+  <dimension ref="A1:C192"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="87.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="87.5" style="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="53"/>
+      <c r="A1" s="52"/>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="53" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="53" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="54"/>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="55" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="56" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="56" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="54"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="55" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="56" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="56" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="56" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="54"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="54"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="55" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="57" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="56" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="56" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="56" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="54"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="56" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="54"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="56" t="s">
+        <v>369</v>
+      </c>
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="56" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="54"/>
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="56" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="56" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="54"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="56" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="56" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="56" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="56" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="56" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="56" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="54"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="56" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="56" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="54"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="56" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="56" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="56" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="54"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="56" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="56" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="56" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="56" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="56" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="56" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="56" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="56" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="56" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="56" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="61" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="56" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="54"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="54"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="55" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="57" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="56" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="56" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="54"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="54"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="55" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="57" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="56" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="56" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="54" t="s">
+    <row r="74" spans="1:1">
+      <c r="A74" s="54"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="54"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="57" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="54" t="s">
+    <row r="80" spans="1:1">
+      <c r="A80" s="56" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="55"/>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="56" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="57" t="s">
+    <row r="81" spans="1:1">
+      <c r="A81" s="58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="58" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="54"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="58" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="58" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="58" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="54"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="58" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="58" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="54"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="58" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="58" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="54"/>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="58" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="58" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="54"/>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="57" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="58" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="58" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="54"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="54"/>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="55" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="57" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="56" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="56" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="56" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="56" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="56" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="57" t="s">
+    <row r="119" spans="1:1">
+      <c r="A119" s="56" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="55"/>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="56" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="57" t="s">
+    <row r="120" spans="1:1">
+      <c r="A120" s="56" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="56" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="56" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="57" t="s">
+    <row r="123" spans="1:1">
+      <c r="A123" s="56" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="57" t="s">
+    <row r="124" spans="1:1">
+      <c r="A124" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="54"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="56" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="55"/>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="55"/>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="56" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="58" t="s">
+    <row r="127" spans="1:1">
+      <c r="A127" s="56" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="57" t="s">
+    <row r="128" spans="1:1">
+      <c r="A128" s="56" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="57" t="s">
+    <row r="129" spans="1:1">
+      <c r="A129" s="56" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="57" t="s">
+    <row r="130" spans="1:1">
+      <c r="A130" s="56" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="55"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="57" t="s">
+    <row r="131" spans="1:1">
+      <c r="A131" s="56" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="54"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="56" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="55"/>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="57" t="s">
+    <row r="134" spans="1:1">
+      <c r="A134" s="56" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="57" t="s">
+    <row r="135" spans="1:1">
+      <c r="A135" s="54"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="56" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="55"/>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="57" t="s">
+    <row r="137" spans="1:1">
+      <c r="A137" s="56" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="57" t="s">
+    <row r="138" spans="1:1">
+      <c r="A138" s="56" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="55"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="57" t="s">
+    <row r="139" spans="1:1">
+      <c r="A139" s="54"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="56" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="57" t="s">
+    <row r="141" spans="1:1">
+      <c r="A141" s="54"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="56" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="57" t="s">
+    <row r="143" spans="1:1">
+      <c r="A143" s="56" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="57" t="s">
+    <row r="144" spans="1:1">
+      <c r="A144" s="56" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="57" t="s">
+    <row r="145" spans="1:1">
+      <c r="A145" s="54"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="54"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="55" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="57" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="57" t="s">
+    <row r="151" spans="1:1">
+      <c r="A151" s="56" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="55"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="57" t="s">
+    <row r="152" spans="1:1">
+      <c r="A152" s="54"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="56" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="57" t="s">
+    <row r="154" spans="1:1">
+      <c r="A154" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="58" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="54"/>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="58" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="58" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="54"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="57" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="55"/>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="57" t="s">
+    <row r="165" spans="1:1">
+      <c r="A165" s="58" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="58" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="54"/>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="56" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="54"/>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="54"/>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="55" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="57" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="57" t="s">
+    <row r="175" spans="1:1">
+      <c r="A175" s="56" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="57" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="55"/>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="57" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="57" t="s">
+    <row r="176" spans="1:1">
+      <c r="A176" s="56" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="57" t="s">
+    <row r="177" spans="1:1">
+      <c r="A177" s="56" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="57" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="57" t="s">
+    <row r="178" spans="1:1">
+      <c r="A178" s="56" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="57" t="s">
+    <row r="179" spans="1:1">
+      <c r="A179" s="56" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="56" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="57" t="s">
+    <row r="181" spans="1:1">
+      <c r="A181" s="54"/>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="54"/>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="55" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="55" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="57" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="57" t="s">
+    <row r="187" spans="1:1">
+      <c r="A187" s="56" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="56" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="57" t="s">
+    <row r="189" spans="1:1">
+      <c r="A189" s="56" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="57" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="57" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" s="57" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="55"/>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="55"/>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="56" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="58" t="s">
+    <row r="190" spans="1:1">
+      <c r="A190" s="56" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="57" t="s">
+    <row r="191" spans="1:1">
+      <c r="A191" s="56" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="57" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="55"/>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="55"/>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="56" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" s="58" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" s="57" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" s="57" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="55"/>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" s="55"/>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" s="56" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" s="58" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" s="57" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="59" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" s="59" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" s="55"/>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" s="59" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="59" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" s="59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="59" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" s="59" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" s="55"/>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" s="59" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" s="59" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="59" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" s="59" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="59" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="55"/>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" s="59" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="59" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="59" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="55"/>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" s="59" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" s="59" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="55"/>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" s="59" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" s="58" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" s="59" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" s="59" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" s="55"/>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" s="55"/>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" s="56" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" s="58" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" s="57" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" s="57" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" s="57" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" s="57" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" s="57" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="57" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" s="57" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" s="57" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="57" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
-      <c r="A123" s="57" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" s="57" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="55"/>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="57" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" s="57" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" s="57" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="57" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" s="57" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" s="57" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" s="55"/>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" s="57" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" s="57" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" s="55"/>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" s="57" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" s="57" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" s="57" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="55"/>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="57" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" s="55"/>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="57" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" s="57" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" s="57" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" s="55"/>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="55"/>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" s="56" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" s="58" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" s="57" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" s="55"/>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" s="57" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" s="59" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" s="59" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="55"/>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" s="59" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" s="59" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="59" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" s="59" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" s="59" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" s="55"/>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" s="59" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" s="58" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" s="59" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="59" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" s="55"/>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" s="57" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="55"/>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="55"/>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" s="56" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" s="58" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" s="57" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="57" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" s="57" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" s="57" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" s="57" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" s="57" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" s="55"/>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" s="55"/>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" s="56" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" s="56" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" s="58" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" s="57" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" s="57" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" s="57" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" s="57" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" s="57" t="s">
-        <v>477</v>
-      </c>
-    </row>
     <row r="192" spans="1:1">
-      <c r="A192" s="60" t="s">
-        <v>394</v>
+      <c r="A192" s="59" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -10935,172 +10398,178 @@
   <sheetData>
     <row r="1" spans="1:1" ht="39">
       <c r="A1" s="6" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28.8">
       <c r="A3" s="8" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="22.2">
       <c r="A4" s="11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="7" t="s">
-        <v>229</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="22.2">
       <c r="A9" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="7" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="28.8">
       <c r="A16" s="8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="28.8">
       <c r="A26" s="8" t="s">
-        <v>145</v>
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="12" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="14"/>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="17" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="28.8">
       <c r="A37" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="20" t="s">
-        <v>234</v>
+        <v>521</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -11109,13 +10578,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="21" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E48" s="16"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="22" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
@@ -11124,57 +10593,57 @@
     </row>
     <row r="53" spans="1:5" ht="28.8">
       <c r="A53" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>362</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="28.8">
       <c r="A63" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -11185,7 +10654,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A3AF8E-8DBC-4068-AF0C-14C73872ECA0}">
-  <dimension ref="A2:A63"/>
+  <dimension ref="A2:C63"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="170.5" style="1" bestFit="1" customWidth="1"/>
@@ -11193,7 +10662,7 @@
   <sheetData>
     <row r="2" spans="1:1" ht="39">
       <c r="A2" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -11201,32 +10670,32 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -11234,103 +10703,109 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="10" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="10" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="10" t="s">
+    <row r="23" spans="1:3">
+      <c r="A23"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="10" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="10" t="s">
+    <row r="26" spans="1:3">
+      <c r="A26" s="10" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="10" t="s">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="10" t="s">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="10" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27"/>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="10" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:3">
       <c r="A32"/>
     </row>
     <row r="33" spans="1:1" ht="39">
       <c r="A33" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -11338,17 +10813,17 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -11356,7 +10831,7 @@
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -11364,7 +10839,7 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -11378,7 +10853,7 @@
     </row>
     <row r="45" spans="1:1" ht="39">
       <c r="A45" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -11386,37 +10861,37 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:1">
@@ -11424,17 +10899,17 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="10" t="s">
-        <v>190</v>
+      <c r="A56" s="31" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -11463,7 +10938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C5F30F-2635-454D-B2E8-BE5E833EC506}">
-  <dimension ref="A2:A31"/>
+  <dimension ref="A2:C56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="35.796875" bestFit="1" customWidth="1"/>
@@ -11534,64 +11009,77 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="28" spans="1:3">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -11602,7 +11090,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F72021E-9D6D-4CA7-A535-34415C2AEFF4}">
-  <dimension ref="A2:A18"/>
+  <dimension ref="A2:C56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="1:1">
@@ -11655,14 +11143,29 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -11673,7 +11176,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1F6E043-60FE-49E2-A806-C2972E8C5770}">
-  <dimension ref="A2:A13"/>
+  <dimension ref="A2:C56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="31.296875" bestFit="1" customWidth="1"/>
@@ -11729,6 +11232,21 @@
         <v>75</v>
       </c>
     </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31" t="s">
+        <v>487</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11737,7 +11255,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A30A62-1DBF-47EA-8D9D-C6F8CBF1B15A}">
-  <dimension ref="A2:D29"/>
+  <dimension ref="A2:D56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.296875" bestFit="1" customWidth="1"/>
@@ -11748,181 +11266,181 @@
   <sheetData>
     <row r="2" spans="1:4">
       <c r="A2" s="28" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="27" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>247</v>
+        <v>489</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="27" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>126</v>
+        <v>489</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="27" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>252</v>
+        <v>524</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="27" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="27" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>258</v>
+        <v>523</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="27" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>262</v>
+        <v>503</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="27" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>354</v>
+        <v>503</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>266</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="27" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>355</v>
+        <v>503</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="27" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B11" t="s">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>357</v>
+        <v>503</v>
       </c>
       <c r="D11" t="s">
-        <v>358</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="27" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="27" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="27" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D14" s="27">
         <v>4000</v>
@@ -11930,212 +11448,220 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="27" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>275</v>
+        <v>495</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="27" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>279</v>
+        <v>497</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="27" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>359</v>
+        <v>498</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="27" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>284</v>
+        <v>497</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="27" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>360</v>
+        <v>498</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="27" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>289</v>
+        <v>499</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="27" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>292</v>
+        <v>499</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="27" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>352</v>
+        <v>500</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="27" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>353</v>
+        <v>501</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="27" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>365</v>
+        <v>525</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="27" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>361</v>
+        <v>502</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>303</v>
+        <v>506</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="27" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>307</v>
+        <v>504</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="27" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>310</v>
+        <v>284</v>
+      </c>
+      <c r="C28" t="s">
+        <v>505</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="27" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>315</v>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="C30" s="65"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -12151,182 +11677,190 @@
   <sheetData>
     <row r="1" spans="1:1" ht="39">
       <c r="A1" s="6" t="s">
-        <v>502</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>503</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="10" t="s">
-        <v>237</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="10" t="s">
-        <v>238</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="10" t="s">
-        <v>239</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="10" t="s">
-        <v>240</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="10" t="s">
-        <v>241</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="22.2">
       <c r="A11" s="11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="39">
+      <c r="A18" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="22.2">
+      <c r="A19" s="11" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="22.2">
+      <c r="A23" s="11" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="7" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="39">
-      <c r="A18" s="6" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="22.2">
-      <c r="A19" s="11" t="s">
+    <row r="25" spans="1:3">
+      <c r="A25" s="7" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="7" t="s">
+    <row r="26" spans="1:3">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="22.2">
+      <c r="A27" s="11" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="7" t="s">
+    <row r="28" spans="1:3">
+      <c r="A28" s="7" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="22.2">
-      <c r="A23" s="11" t="s">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="7" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="7" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="22.2">
-      <c r="A27" s="11" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="7" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="39">
       <c r="A33" s="6" t="s">
-        <v>505</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="22.2">
       <c r="A34" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="10" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="22.2">
       <c r="A37" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="10" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="10" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="22.2">
       <c r="A43" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="23" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="39">
       <c r="A49" s="6" t="s">
-        <v>506</v>
+        <v>460</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="8" t="s">
-        <v>507</v>
+        <v>461</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="24" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -12338,62 +11872,62 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="29" t="s">
-        <v>321</v>
+      <c r="A56" s="63" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="29" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="29" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="29" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="29" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="29" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="29" t="s">
-        <v>319</v>
+        <v>492</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="29" t="s">
-        <v>326</v>
+        <v>496</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="29" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="28.8">
       <c r="A66" s="8" t="s">
-        <v>508</v>
+        <v>462</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="20" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
@@ -12402,7 +11936,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="22" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
@@ -12411,101 +11945,101 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="29" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="29" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="29" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="29" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="29" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="29" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="29" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="29" t="s">
-        <v>329</v>
+        <v>301</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="29" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="29" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="19.8" customHeight="1">
       <c r="A80" s="29" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="H80" s="8"/>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="7" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="7" t="s">
-        <v>333</v>
+        <v>493</v>
       </c>
       <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="7" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="H83" s="7"/>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="29"/>
-      <c r="B84" s="31" t="s">
-        <v>338</v>
+      <c r="B84" s="10" t="s">
+        <v>497</v>
       </c>
       <c r="H84" s="7"/>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="29"/>
-      <c r="B85" s="31" t="s">
-        <v>282</v>
+      <c r="B85" s="10" t="s">
+        <v>498</v>
       </c>
       <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="7" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="H86" s="7"/>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="7" t="s">
-        <v>336</v>
+        <v>307</v>
       </c>
       <c r="H87" s="7"/>
     </row>
@@ -12515,19 +12049,19 @@
     </row>
     <row r="89" spans="1:8" ht="22.2">
       <c r="A89" s="11" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H89" s="30"/>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H90" s="7"/>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H91" s="7"/>
     </row>
@@ -12536,12 +12070,12 @@
     </row>
     <row r="93" spans="1:8" ht="28.8">
       <c r="A93" s="8" t="s">
-        <v>509</v>
+        <v>463</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="24" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B94" s="25"/>
       <c r="C94" s="25"/>
@@ -12550,242 +12084,242 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>339</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>343</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="B102" t="s">
-        <v>279</v>
+        <v>497</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="B103" t="s">
-        <v>282</v>
+        <v>498</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="28.8">
       <c r="A107" s="8" t="s">
-        <v>510</v>
+        <v>464</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>339</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>343</v>
+        <v>494</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="B114" t="s">
-        <v>279</v>
+        <v>497</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="B115" t="s">
-        <v>282</v>
+        <v>498</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="39">
       <c r="A120" s="6" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="61" t="s">
-        <v>512</v>
+      <c r="A121" s="60" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="10" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="10" t="s">
-        <v>515</v>
+        <v>468</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="10" t="s">
-        <v>516</v>
+        <v>469</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="10" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="10" t="s">
-        <v>518</v>
+        <v>470</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="10" t="s">
-        <v>519</v>
+        <v>471</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="10" t="s">
-        <v>533</v>
+        <v>483</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="10" t="s">
-        <v>520</v>
+        <v>472</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="10" t="s">
-        <v>521</v>
+        <v>473</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="10" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="10" t="s">
-        <v>524</v>
+        <v>475</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="10" t="s">
-        <v>523</v>
+        <v>474</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="10" t="s">
-        <v>525</v>
+        <v>476</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="10" t="s">
-        <v>526</v>
+        <v>477</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="10" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="10" t="s">
-        <v>533</v>
+        <v>483</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="10" t="s">
-        <v>534</v>
+        <v>484</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="10" t="s">
-        <v>528</v>
+        <v>479</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="10" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="10" t="s">
-        <v>529</v>
+        <v>480</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="10" t="s">
-        <v>531</v>
+        <v>481</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="10" t="s">
-        <v>532</v>
+        <v>482</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="10" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="61" t="s">
-        <v>535</v>
+      <c r="A146" s="60" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -12796,7 +12330,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE1B2BA-3062-41ED-AC91-89D47F0FAC2F}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="23.09765625" bestFit="1" customWidth="1"/>
@@ -12810,141 +12344,159 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="1:7" ht="18.600000000000001" thickBot="1">
-      <c r="A2" s="45" t="s">
-        <v>478</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>480</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>481</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="F2" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>484</v>
+      <c r="A2" s="44" t="s">
+        <v>435</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>438</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="33" t="s">
-        <v>347</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>485</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>486</v>
-      </c>
-      <c r="D3" s="34" t="s">
+      <c r="A3" s="32" t="s">
+        <v>526</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>442</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>443</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>444</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>445</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="35" t="s">
+        <v>526</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>449</v>
+      </c>
+      <c r="E4" s="42">
+        <v>443</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>526</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.600000000000001" thickBot="1">
+      <c r="A5" s="38" t="s">
+        <v>526</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>443</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>444</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="G5" s="40" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="E6" s="41">
+        <v>443</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>453</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.600000000000001" thickBot="1">
+      <c r="A7" s="38" t="s">
+        <v>527</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>447</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>444</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>451</v>
+      </c>
+      <c r="G7" s="40" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="66"/>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="31" t="s">
         <v>487</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>487</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>488</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="36" t="s">
-        <v>347</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>490</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>491</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>492</v>
-      </c>
-      <c r="E4" s="43">
-        <v>443</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>493</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.600000000000001" thickBot="1">
-      <c r="A5" s="39" t="s">
-        <v>347</v>
-      </c>
-      <c r="B5" s="40" t="s">
-        <v>490</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>486</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>487</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>487</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>495</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="33" t="s">
-        <v>497</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>485</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>491</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>492</v>
-      </c>
-      <c r="E6" s="42">
-        <v>443</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>498</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.600000000000001" thickBot="1">
-      <c r="A7" s="39" t="s">
-        <v>497</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>490</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>486</v>
-      </c>
-      <c r="D7" s="40" t="s">
-        <v>487</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>487</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>495</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -12955,135 +12507,140 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6411A21-FB54-4564-8B85-66C6F914DA79}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="38.296875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="48" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="48" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="48" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="48" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="48" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="48" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="48" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="48" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="49" t="s">
+    <row r="14" spans="1:1">
+      <c r="A14" s="48" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="49" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="48" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="48" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="49" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="48" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="48" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="48" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="48" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="49" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="49" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="49" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="49" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="49" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="49" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="49" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="49" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="49" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="50" t="s">
-        <v>115</v>
+    <row r="56" spans="1:1">
+      <c r="A56" s="62" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -13094,76 +12651,79 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{253981ED-5B4A-4921-8D3C-CBBC5366F1F6}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="45.09765625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="48" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="48" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="49" t="s">
-        <v>116</v>
+      <c r="A7" s="48" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="49" t="s">
-        <v>117</v>
+      <c r="A8" s="48" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="48" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="49" t="s">
-        <v>118</v>
+      <c r="A10" s="48" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="48" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="49" t="s">
-        <v>114</v>
+      <c r="A12" s="48" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="50" t="s">
-        <v>115</v>
-      </c>
+      <c r="A13" s="49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="62"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
